--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486520_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486520_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7719</v>
+        <v>4.2018</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9024</v>
+        <v>1.2697</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8694</v>
+        <v>2.9321</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2207</v>
+        <v>-0.871</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.463</v>
+        <v>1.0557</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2423</v>
+        <v>-1.9268</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5079</v>
+        <v>-0.2605</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4316</v>
+        <v>2.2026</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9395</v>
+        <v>-2.463</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7285</v>
+        <v>-0.6106</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0313</v>
+        <v>-1.1468</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3028</v>
+        <v>0.5362</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2626</v>
+        <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6222</v>
+        <v>0.441</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2869</v>
+        <v>0.4002</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3354</v>
+        <v>0.0408</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1952</v>
+        <v>2.2393</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.1093</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4577</v>
+        <v>4.0708</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7722</v>
+        <v>1.1706</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6855</v>
+        <v>2.9003</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.871</v>
+        <v>-0.2207</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0557</v>
+        <v>-1.463</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.9268</v>
+        <v>1.2423</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2605</v>
+        <v>0.5079</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2026</v>
+        <v>-0.4316</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.463</v>
+        <v>0.9395</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6106</v>
+        <v>-0.7285</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1468</v>
+        <v>-1.0313</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5362</v>
+        <v>0.3028</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3926</v>
+        <v>3.2626</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3031</v>
+        <v>1.9212</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0973</v>
+        <v>1.555</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2057</v>
+        <v>0.3662</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2393</v>
+        <v>0.1952</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9497</v>
+        <v>2.2146</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3692</v>
+        <v>2.3259</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4195</v>
+        <v>-0.1113</v>
       </c>
       <c r="G4" t="n">
         <v>1.4508</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3461</v>
+        <v>0.6111</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2896</v>
+        <v>0.2464</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0565</v>
+        <v>0.3647</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9347</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0235</v>
+        <v>0.5814</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6407</v>
+        <v>-0.2369</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6642</v>
+        <v>0.8183</v>
       </c>
       <c r="G5" t="n">
         <v>-0.6155</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2962</v>
+        <v>0.2617</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1694</v>
+        <v>0.2343</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1268</v>
+        <v>0.0273</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3698</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. ZURBRIGGEN</t>
+          <t>P. MOLINS CALDERON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3506</v>
+        <v>-0.6367</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.0722</v>
+        <v>0.0582</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7216</v>
+        <v>-0.695</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4307</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0609</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4916</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8058999999999999</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2618</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.0678</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3752</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2009</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5760999999999999</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-4.5676</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.5252</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3226</v>
+        <v>-0.137</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8038</v>
+        <v>-0.137</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5188</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3252</v>
+        <v>-0.9347</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4552</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
         <v>-1.13</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MOLINS CALDERON</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6367</v>
+        <v>-1.0135</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0582</v>
+        <v>-2.4738</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.695</v>
+        <v>1.4603</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-3.0648</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.6963</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-3.7611</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-1.8741</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.2957</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-3.1698</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-1.1907</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.5994</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.5913</v>
       </c>
       <c r="P7" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.137</v>
+        <v>0.9638</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.137</v>
+        <v>0.4879</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.4759</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3077</v>
+        <v>-1.6653</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0145</v>
+        <v>-1.8181</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7068</v>
+        <v>0.1528</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.0648</v>
+        <v>-0.7319</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6963</v>
+        <v>-0.7239</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.7611</v>
+        <v>-0.008</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8741</v>
+        <v>0.1719</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2957</v>
+        <v>0.438</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.1698</v>
+        <v>-0.2661</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1907</v>
+        <v>-0.9038</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5994</v>
+        <v>-1.1619</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5913</v>
+        <v>0.2582</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>-0.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6696</v>
+        <v>-0.0634</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0529</v>
+        <v>0.1851</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7224</v>
+        <v>-0.2485</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. ROTEGARD</t>
+          <t>F. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0042</v>
+        <v>-1.7549</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0382</v>
+        <v>-3.8293</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0424</v>
+        <v>2.0743</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0382</v>
+        <v>-0.4307</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.0609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0382</v>
+        <v>-0.4916</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0382</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.2618</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0382</v>
+        <v>-1.0678</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.3752</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.2009</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2175</v>
+        <v>-4.5676</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-6.5252</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.9182</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.0467</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.2599</v>
+        <v>1.3252</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2623</v>
+        <v>-1.8324</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.013</v>
+        <v>-2.4289</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7507</v>
+        <v>0.5966</v>
       </c>
       <c r="G10" t="n">
         <v>0.2468</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1388</v>
+        <v>0.2911</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3869</v>
+        <v>0.1971</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2481</v>
+        <v>0.094</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>T. ROTEGARD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4651</v>
+        <v>-2.0042</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4022</v>
+        <v>0.0382</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0629</v>
+        <v>-2.0424</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7319</v>
+        <v>0.0382</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7239</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.008</v>
+        <v>0.0382</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1719</v>
+        <v>0.0382</v>
       </c>
       <c r="K11" t="n">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2661</v>
+        <v>0.0382</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9038</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1619</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2582</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8632</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.399</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4642</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6359</v>
+        <v>-2.3246</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5458</v>
+        <v>-2.1421</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.09</v>
+        <v>-0.1825</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9102</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0737</v>
+        <v>0.2376</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.125</v>
+        <v>0.2788</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0513</v>
+        <v>-0.0412</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8695</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6378</v>
+        <v>-2.5646</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9496</v>
+        <v>-1.0613</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6882</v>
+        <v>-1.5033</v>
       </c>
       <c r="G13" t="n">
         <v>-1.174</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4694</v>
+        <v>0.5426</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3461</v>
+        <v>0.2343</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1233</v>
+        <v>0.3082</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7156</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.0975</v>
+        <v>-2.7276</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.4978</v>
+        <v>-9.127800000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>6.400199999999998</v>
+        <v>6.4002</v>
       </c>
       <c r="G14" t="n">
         <v>-6.282999999999999</v>
@@ -1537,7 +1537,7 @@
         <v>2.2589</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0875</v>
+        <v>1.087500000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.3129</v>
@@ -1546,13 +1546,13 @@
         <v>17.4004</v>
       </c>
       <c r="S14" t="n">
-        <v>5.617900000000001</v>
+        <v>6.987900000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3589</v>
+        <v>4.728800000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2591</v>
+        <v>2.2589</v>
       </c>
       <c r="V14" t="n">
         <v>-4.5197</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7742</v>
+        <v>7.9856</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5725</v>
+        <v>4.1313</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2017</v>
+        <v>3.8543</v>
       </c>
       <c r="G15" t="n">
         <v>4.9525</v>
@@ -1624,13 +1624,13 @@
         <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0038</v>
+        <v>0.2076</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.2391</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2059</v>
+        <v>0.4467</v>
       </c>
       <c r="V15" t="n">
         <v>1.5204</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.0131</v>
+        <v>5.0849</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2177</v>
+        <v>2.7706</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7954</v>
+        <v>2.3143</v>
       </c>
       <c r="G16" t="n">
         <v>2.4944</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2209</v>
+        <v>-0.149</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1406</v>
+        <v>-0.3064</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3615</v>
+        <v>0.1574</v>
       </c>
       <c r="V16" t="n">
         <v>1.8695</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6342</v>
+        <v>2.565</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4784</v>
+        <v>-0.5224</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1558</v>
+        <v>3.0874</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.962</v>
+        <v>-0.3311</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0851</v>
+        <v>1.022</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0471</v>
+        <v>-1.3531</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6742</v>
+        <v>-1.6649</v>
       </c>
       <c r="K17" t="n">
-        <v>0.949</v>
+        <v>0.6268</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.6232</v>
+        <v>-2.2917</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2878</v>
+        <v>1.3338</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8639</v>
+        <v>0.3951</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.9387</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5087</v>
+        <v>0.2659</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0227</v>
+        <v>0.0349</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.514</v>
+        <v>0.231</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8381</v>
+        <v>2.3454</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3427</v>
+        <v>2.4544</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5046</v>
+        <v>-0.109</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8088</v>
@@ -1858,13 +1858,13 @@
         <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7006</v>
+        <v>-1.1933</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.822</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8787</v>
+        <v>-0.4831</v>
       </c>
       <c r="V18" t="n">
         <v>2.8249</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1944</v>
+        <v>2.3067</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0812</v>
+        <v>0.9196</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2756</v>
+        <v>1.3871</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3311</v>
+        <v>-0.962</v>
       </c>
       <c r="H19" t="n">
-        <v>1.022</v>
+        <v>0.0851</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3531</v>
+        <v>-1.0471</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6649</v>
+        <v>-0.6742</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6268</v>
+        <v>0.949</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.2917</v>
+        <v>-1.6232</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3338</v>
+        <v>-0.2878</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3951</v>
+        <v>-0.8639</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9387</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1047</v>
+        <v>0.1812</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5239</v>
+        <v>0.4639</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5808</v>
+        <v>-0.2827</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.1771</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0827</v>
+        <v>-1.2003</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7504999999999999</v>
+        <v>1.3774</v>
       </c>
       <c r="G20" t="n">
         <v>0.3714</v>
@@ -2014,13 +2014,13 @@
         <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7091</v>
+        <v>0.2184</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6992</v>
+        <v>0.5816</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9901</v>
+        <v>-0.3632</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1952</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4576</v>
+        <v>-1.2225</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7093</v>
+        <v>-0.5976</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7482</v>
+        <v>-0.6249</v>
       </c>
       <c r="G21" t="n">
         <v>0.1883</v>
@@ -2092,13 +2092,13 @@
         <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7758</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3648</v>
+        <v>-0.2415</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. LEVY</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3062</v>
+        <v>-2.3883</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6391</v>
+        <v>-5.0379</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6671</v>
+        <v>2.6495</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6026</v>
+        <v>1.2348</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4719</v>
+        <v>0.5503</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1307</v>
+        <v>0.6845</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4336</v>
+        <v>0.0549</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4719</v>
+        <v>0.5871</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0382</v>
+        <v>-0.5323</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1689</v>
+        <v>1.18</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.0368</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1689</v>
+        <v>1.2168</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-4.7852</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4264</v>
+        <v>0.1169</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2055</v>
+        <v>-0.3076</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6318</v>
+        <v>0.4245</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>G. LEVY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5056</v>
+        <v>-2.676</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.8846</v>
+        <v>-1.6391</v>
       </c>
       <c r="F23" t="n">
-        <v>3.379</v>
+        <v>-1.0369</v>
       </c>
       <c r="G23" t="n">
-        <v>0.773</v>
+        <v>-1.6026</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1553</v>
+        <v>-1.4719</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9283</v>
+        <v>-0.1307</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1265</v>
+        <v>-1.4336</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6935</v>
+        <v>-1.4719</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.8199</v>
+        <v>0.0382</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8994</v>
+        <v>-0.1689</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8488</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.7483</v>
+        <v>-0.1689</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.6976</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.8727</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1751</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3205</v>
+        <v>0.0565</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0154</v>
+        <v>-0.2055</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6949</v>
+        <v>0.262</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8469</v>
+        <v>-2.7688</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0178</v>
+        <v>-5.7728</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8291</v>
+        <v>3.004</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0269</v>
+        <v>0.773</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2895</v>
+        <v>-0.1553</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3164</v>
+        <v>0.9283</v>
       </c>
       <c r="J24" t="n">
-        <v>0.876</v>
+        <v>-0.1265</v>
       </c>
       <c r="K24" t="n">
-        <v>0.876</v>
+        <v>0.6935</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.8199</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9029</v>
+        <v>0.8994</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4136</v>
+        <v>-0.8488</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3164</v>
+        <v>1.7483</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6525</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.305</v>
+        <v>-5.8727</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6525</v>
+        <v>2.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.733</v>
+        <v>-0.5837</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4795</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2536</v>
+        <v>0.3199</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.4345</v>
+        <v>0.7395</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.1093</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3252</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.908</v>
+        <v>-3.5862</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.5967</v>
+        <v>-1.9061</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6887</v>
+        <v>-1.6801</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2348</v>
+        <v>-0.0269</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5503</v>
+        <v>1.2895</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6845</v>
+        <v>-1.3164</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0549</v>
+        <v>0.876</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5871</v>
+        <v>0.876</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5323</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.18</v>
+        <v>-0.9029</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0368</v>
+        <v>0.4136</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2168</v>
+        <v>-1.3164</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.6101</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.7852</v>
+        <v>-1.305</v>
       </c>
       <c r="R25" t="n">
-        <v>2.1751</v>
+        <v>0.6525</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4027</v>
+        <v>-0.4723</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.3677</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5363</v>
+        <v>-0.1046</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.13</v>
+        <v>-2.4345</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-1.1093</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="26">
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4.0975</v>
+        <v>7.822899999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.4001</v>
+        <v>-6.4003</v>
       </c>
       <c r="F26" t="n">
-        <v>10.4977</v>
+        <v>14.2231</v>
       </c>
       <c r="G26" t="n">
         <v>6.282999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>2.980300000000001</v>
+        <v>2.9803</v>
       </c>
       <c r="I26" t="n">
         <v>3.3029</v>
@@ -2467,13 +2467,13 @@
         <v>1.5606</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.0013</v>
+        <v>-4.001300000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>5.562</v>
+        <v>5.562000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.0876</v>
+        <v>-1.087600000000001</v>
       </c>
       <c r="Q26" t="n">
         <v>-17.4005</v>
@@ -2482,16 +2482,16 @@
         <v>16.3131</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.6178</v>
+        <v>-1.8926</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.2591</v>
+        <v>-2.259</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.359</v>
+        <v>0.3663999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>4.519799999999999</v>
+        <v>4.5198</v>
       </c>
       <c r="W26" t="n">
         <v>8.536900000000001</v>
